--- a/01_INPUTS/objccc.xlsx
+++ b/01_INPUTS/objccc.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Orbit\MATINAL_PENAFLOR\01_INPUTS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF920486-CB0C-4954-99E7-680A14CDA110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788920C1-6AE3-4A4F-8CA4-5343AAF10EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{472D008F-7292-4943-B105-A39854C23553}"/>
   </bookViews>
   <sheets>
     <sheet name="total" sheetId="1" r:id="rId1"/>
@@ -112,7 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +148,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="6">
@@ -316,10 +323,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -357,9 +365,15 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -699,7 +713,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="5">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -707,7 +721,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="4">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -715,7 +729,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="5">
-        <v>145</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -723,7 +737,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="6">
-        <v>845</v>
+        <v>645</v>
       </c>
     </row>
   </sheetData>
@@ -733,14 +747,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DB081E0-9AE7-4DAB-9890-F61695A71426}">
-  <dimension ref="A2:C9"/>
+  <dimension ref="A2:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="11"/>
     <col min="2" max="2" width="28.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>22</v>
       </c>
@@ -748,10 +762,10 @@
         <v>14</v>
       </c>
       <c r="C2" s="12">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="11" t="s">
         <v>15</v>
       </c>
@@ -759,10 +773,12 @@
         <v>7</v>
       </c>
       <c r="C3" s="8">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="16"/>
+    </row>
+    <row r="4" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
         <v>16</v>
       </c>
@@ -772,8 +788,10 @@
       <c r="C4" s="9">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F4" s="15"/>
+      <c r="G4" s="16"/>
+    </row>
+    <row r="5" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>17</v>
       </c>
@@ -781,10 +799,12 @@
         <v>9</v>
       </c>
       <c r="C5" s="9">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="16"/>
+    </row>
+    <row r="6" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
@@ -792,10 +812,12 @@
         <v>10</v>
       </c>
       <c r="C6" s="9">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+    </row>
+    <row r="7" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>19</v>
       </c>
@@ -803,10 +825,12 @@
         <v>11</v>
       </c>
       <c r="C7" s="9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+      <c r="F7" s="15"/>
+      <c r="G7" s="16"/>
+    </row>
+    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
@@ -814,10 +838,12 @@
         <v>12</v>
       </c>
       <c r="C8" s="9">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="F8" s="15"/>
+      <c r="G8" s="16"/>
+    </row>
+    <row r="9" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>21</v>
       </c>
@@ -825,8 +851,10 @@
         <v>13</v>
       </c>
       <c r="C9" s="9">
-        <v>29</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -836,13 +864,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4AD47348-85A2-4C18-8DA4-92C2AF2609CC}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
         <v>22</v>
       </c>
@@ -850,10 +878,10 @@
         <v>14</v>
       </c>
       <c r="D2" s="6">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
@@ -861,10 +889,12 @@
         <v>7</v>
       </c>
       <c r="D3" s="13">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
@@ -872,10 +902,12 @@
         <v>8</v>
       </c>
       <c r="D4" s="14">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+      <c r="G4" s="15"/>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
@@ -883,10 +915,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="14">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="17"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>18</v>
       </c>
@@ -894,10 +928,12 @@
         <v>10</v>
       </c>
       <c r="D6" s="14">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="17"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
@@ -905,10 +941,12 @@
         <v>11</v>
       </c>
       <c r="D7" s="14">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>20</v>
       </c>
@@ -916,10 +954,12 @@
         <v>12</v>
       </c>
       <c r="D8" s="14">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>21</v>
       </c>
@@ -927,8 +967,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="14">
-        <v>117</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -937,14 +979,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06FA2B96-E5F9-4515-B59B-7A1A903884DB}">
-  <dimension ref="B2:D9"/>
+  <dimension ref="B2:H9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13" customWidth="1"/>
     <col min="3" max="3" width="32.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="11" t="s">
         <v>22</v>
       </c>
@@ -952,10 +994,10 @@
         <v>14</v>
       </c>
       <c r="D2" s="10">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="11" t="s">
         <v>15</v>
       </c>
@@ -963,10 +1005,12 @@
         <v>7</v>
       </c>
       <c r="D3" s="10">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+    </row>
+    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B4" s="11" t="s">
         <v>16</v>
       </c>
@@ -976,8 +1020,10 @@
       <c r="D4" s="10">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G4" s="15"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
         <v>17</v>
       </c>
@@ -985,10 +1031,12 @@
         <v>9</v>
       </c>
       <c r="D5" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="16"/>
+    </row>
+    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="11" t="s">
         <v>18</v>
       </c>
@@ -996,10 +1044,12 @@
         <v>10</v>
       </c>
       <c r="D6" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>11</v>
+      </c>
+      <c r="G6" s="15"/>
+      <c r="H6" s="16"/>
+    </row>
+    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="11" t="s">
         <v>19</v>
       </c>
@@ -1007,10 +1057,12 @@
         <v>11</v>
       </c>
       <c r="D7" s="10">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="16"/>
+    </row>
+    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="11" t="s">
         <v>20</v>
       </c>
@@ -1018,10 +1070,12 @@
         <v>12</v>
       </c>
       <c r="D8" s="10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4</v>
+      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
+    </row>
+    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="11" t="s">
         <v>21</v>
       </c>
@@ -1029,8 +1083,10 @@
         <v>13</v>
       </c>
       <c r="D9" s="10">
-        <v>12</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="G9" s="15"/>
+      <c r="H9" s="16"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
